--- a/ig/DM-JUIN-2026/ValueSet-JDV-J60-FormatCode-DMP.xlsx
+++ b/ig/DM-JUIN-2026/ValueSet-JDV-J60-FormatCode-DMP.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="152">
   <si>
     <t>Property</t>
   </si>
@@ -381,6 +381,12 @@
     <t>Test rapide d'orientation diagnostique</t>
   </si>
   <si>
+    <t>urn:asip#urn:ihe:iti-fr:xds-sd:jpeg:2010</t>
+  </si>
+  <si>
+    <t>Document à corps non structuré en format jpeg</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -414,24 +420,6 @@
     <t>Dispensation médicamenteuse</t>
   </si>
   <si>
-    <t>urn:ihe:iti-fr:xds-sd:jpeg:2010</t>
-  </si>
-  <si>
-    <t>Document à corps non structuré en format jpeg</t>
-  </si>
-  <si>
-    <t>urn:ihe:iti-fr:xds-sd:rtf:2010</t>
-  </si>
-  <si>
-    <t>Document à corps non structuré en format rtf</t>
-  </si>
-  <si>
-    <t>urn:ihe:iti-fr:xds-sd:tiff:2010</t>
-  </si>
-  <si>
-    <t>Document à corps non structuré en format tiff</t>
-  </si>
-  <si>
     <t>urn:ihe:lab:xd-lab:2008</t>
   </si>
   <si>
@@ -471,7 +459,7 @@
     <t>1.2.840.10008.5.1.4.1.1.88.59</t>
   </si>
   <si>
-    <t>Document Références d'objets d'un examen d'imagerie selon profil IHE RAD XDS-I</t>
+    <t>Key Object Selection Document Storage</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_A09-DICOMuidRegistry/FHIR/TRE-A09-DICOMuidRegistry</t>
@@ -745,7 +733,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:B51"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1141,15 +1129,23 @@
         <v>121</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>123</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -1159,7 +1155,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1176,122 +1172,98 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>137</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>91</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>144</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="B13" t="s" s="2">
         <v>145</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -1318,26 +1290,26 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -1364,26 +1336,26 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM-JUIN-2026/ValueSet-JDV-J60-FormatCode-DMP.xlsx
+++ b/ig/DM-JUIN-2026/ValueSet-JDV-J60-FormatCode-DMP.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-27T12:00:00+01:00</t>
+    <t>2026-06-15T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JUIN-2026/ValueSet-JDV-J60-FormatCode-DMP.xlsx
+++ b/ig/DM-JUIN-2026/ValueSet-JDV-J60-FormatCode-DMP.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="156">
   <si>
     <t>Property</t>
   </si>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:00:00+01:00</t>
+    <t>2024-09-27T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -381,43 +381,55 @@
     <t>Test rapide d'orientation diagnostique</t>
   </si>
   <si>
-    <t>urn:asip#urn:ihe:iti-fr:xds-sd:jpeg:2010</t>
+    <t/>
+  </si>
+  <si>
+    <t>System URI</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_A06-FormatCodeComplementaire/FHIR/TRE-A06-FormatCodeComplementaire</t>
+  </si>
+  <si>
+    <t>urn:ihe:iti:dsg:detached:2014</t>
+  </si>
+  <si>
+    <t>Signature détachée</t>
+  </si>
+  <si>
+    <t>urn:ihe:iti:xds-sd:pdf:2008</t>
+  </si>
+  <si>
+    <t>Document à corps non structuré en Pdf/A-1</t>
+  </si>
+  <si>
+    <t>urn:ihe:iti:xds-sd:text:2008</t>
+  </si>
+  <si>
+    <t>Document à corps non structuré en texte brut</t>
+  </si>
+  <si>
+    <t>urn:ihe:pharm:dis:2010</t>
+  </si>
+  <si>
+    <t>Dispensation médicamenteuse</t>
+  </si>
+  <si>
+    <t>urn:ihe:iti-fr:xds-sd:jpeg:2010</t>
   </si>
   <si>
     <t>Document à corps non structuré en format jpeg</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>System URI</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_A06-FormatCodeComplementaire/FHIR/TRE-A06-FormatCodeComplementaire</t>
-  </si>
-  <si>
-    <t>urn:ihe:iti:dsg:detached:2014</t>
-  </si>
-  <si>
-    <t>Signature détachée</t>
-  </si>
-  <si>
-    <t>urn:ihe:iti:xds-sd:pdf:2008</t>
-  </si>
-  <si>
-    <t>Document à corps non structuré en Pdf/A-1</t>
-  </si>
-  <si>
-    <t>urn:ihe:iti:xds-sd:text:2008</t>
-  </si>
-  <si>
-    <t>Document à corps non structuré en texte brut</t>
-  </si>
-  <si>
-    <t>urn:ihe:pharm:dis:2010</t>
-  </si>
-  <si>
-    <t>Dispensation médicamenteuse</t>
+    <t>urn:ihe:iti-fr:xds-sd:rtf:2010</t>
+  </si>
+  <si>
+    <t>Document à corps non structuré en format rtf</t>
+  </si>
+  <si>
+    <t>urn:ihe:iti-fr:xds-sd:tiff:2010</t>
+  </si>
+  <si>
+    <t>Document à corps non structuré en format tiff</t>
   </si>
   <si>
     <t>urn:ihe:lab:xd-lab:2008</t>
@@ -459,7 +471,7 @@
     <t>1.2.840.10008.5.1.4.1.1.88.59</t>
   </si>
   <si>
-    <t>Key Object Selection Document Storage</t>
+    <t>Document Références d'objets d'un examen d'imagerie selon profil IHE RAD XDS-I</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_A09-DICOMuidRegistry/FHIR/TRE-A09-DICOMuidRegistry</t>
@@ -733,7 +745,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B51"/>
+  <dimension ref="A1:B50"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1129,23 +1141,15 @@
         <v>121</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>123</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -1155,7 +1159,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1172,98 +1176,122 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>91</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>139</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>140</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>142</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>144</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>123</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -1290,26 +1318,26 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -1336,26 +1364,26 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
